--- a/textbook_examples/mod01_sum.xlsx
+++ b/textbook_examples/mod01_sum.xlsx
@@ -1,81 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2B591B77D510A2C81D1EDAD344C7E8F05C65E640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SUM example" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SUM example" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Ranges and the SUM function</t>
+  </si>
+  <si>
+    <t>Five fields of wheat.  Column B is the size of each field in acres and column C is its yield in bushels per acre.  Multiplying the two gives the bushels each field produced (column D).  To add those up we hand SUM a range — D5:D9 — rather than writing D5+D6+D7+D8+D9.</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Acres</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>Bushels</t>
+  </si>
+  <si>
+    <t>The formula in D</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Creek</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Rented</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Other ways to give SUM a range</t>
+  </si>
+  <si>
+    <t>One column</t>
+  </si>
+  <si>
+    <t>The five acre figures, B5 down to B9.</t>
+  </si>
+  <si>
+    <t>One row</t>
+  </si>
+  <si>
+    <t>Straight across row 5 — acres, yield and bushels. Rarely what you want.</t>
+  </si>
+  <si>
+    <t>Two ranges at once</t>
+  </si>
+  <si>
+    <t>Separate ranges with a comma.</t>
+  </si>
+  <si>
+    <t>A range plus a number</t>
+  </si>
+  <si>
+    <t>Adds 40 acres of summerfallow that is not in the table.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF4A7C59"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="14"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF5C6B62"/>
       <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
       <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF2F5D46"/>
       <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="FF4A7C59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="FFF6EFD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,104 +186,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -476,276 +514,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ranges and the SUM function</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Five fields of wheat.  Column B is the size of each field in acres and column C is its yield in bushels per acre.  Multiplying the two gives the bushels each field produced (column D).  To add those up we hand SUM a range — D5:D9 — rather than writing D5+D6+D7+D8+D9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Acres</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Bushels</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5">
         <v>120</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="6">
         <v>52.4</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="8">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+        <v>6288</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <f t="shared" ref="E5:E10" ca="1" si="0">_xlfn.FORMULATEXT(D5)</f>
+        <v>=B5*C5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5">
         <v>240</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6">
         <v>48.9</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="8">
-        <f>_xlfn.FORMULATEXT(D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Creek</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
+        <v>11736</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B6*C6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5">
         <v>95</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6">
         <v>61.2</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
+        <v>5814</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B7*C7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5">
         <v>310</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6">
         <v>55.7</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="8">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Rented</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
+        <v>17267</v>
+      </c>
+      <c r="E8" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B8*C8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5">
         <v>175</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6">
         <v>44.3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="8">
-        <f>_xlfn.FORMULATEXT(D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
+        <v>7752.4999999999991</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B9*C9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9">
         <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
+        <v>940</v>
+      </c>
+      <c r="D10" s="9">
         <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>_xlfn.FORMULATEXT(D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Other ways to give SUM a range</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>One column</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
+        <v>48857.5</v>
+      </c>
+      <c r="E10" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=SUM(D5:D9)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="5">
         <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C13" s="8">
-        <f>_xlfn.FORMULATEXT(B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>The five acre figures, B5 down to B9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>One row</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
+        <v>940</v>
+      </c>
+      <c r="C13" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B13)</f>
+        <v>=SUM(B5:B9)</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5">
         <f>SUM(B5:D5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="8">
-        <f>_xlfn.FORMULATEXT(B14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Straight across row 5 — acres, yield and bushels. Rarely what you want.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Two ranges at once</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
+        <v>6460.4</v>
+      </c>
+      <c r="C14" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B14)</f>
+        <v>=SUM(B5:D5)</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="5">
         <f>SUM(B5:B9,D5:D9)</f>
-        <v/>
-      </c>
-      <c r="C15" s="8">
-        <f>_xlfn.FORMULATEXT(B15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Separate ranges with a comma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A range plus a number</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
+        <v>49797.5</v>
+      </c>
+      <c r="C15" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B15)</f>
+        <v>=SUM(B5:B9,D5:D9)</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="5">
         <f>SUM(B5:B9,40)</f>
-        <v/>
-      </c>
-      <c r="C16" s="8">
-        <f>_xlfn.FORMULATEXT(B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Adds 40 acres of summerfallow that is not in the table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
+        <v>980</v>
+      </c>
+      <c r="C16" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B16)</f>
+        <v>=SUM(B5:B9,40)</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C16:D16"/>

--- a/textbook_examples/mod01_sum.xlsx
+++ b/textbook_examples/mod01_sum.xlsx
@@ -1,176 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B591B77D510A2C81D1EDAD344C7E8F05C65E640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SUM example" sheetId="1" r:id="rId1"/>
+    <sheet name="SUM example" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Ranges and the SUM function</t>
-  </si>
-  <si>
-    <t>Five fields of wheat.  Column B is the size of each field in acres and column C is its yield in bushels per acre.  Multiplying the two gives the bushels each field produced (column D).  To add those up we hand SUM a range — D5:D9 — rather than writing D5+D6+D7+D8+D9.</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Acres</t>
-  </si>
-  <si>
-    <t>Yield (bu/ac)</t>
-  </si>
-  <si>
-    <t>Bushels</t>
-  </si>
-  <si>
-    <t>The formula in D</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>Creek</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Rented</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Other ways to give SUM a range</t>
-  </si>
-  <si>
-    <t>One column</t>
-  </si>
-  <si>
-    <t>The five acre figures, B5 down to B9.</t>
-  </si>
-  <si>
-    <t>One row</t>
-  </si>
-  <si>
-    <t>Straight across row 5 — acres, yield and bushels. Rarely what you want.</t>
-  </si>
-  <si>
-    <t>Two ranges at once</t>
-  </si>
-  <si>
-    <t>Separate ranges with a comma.</t>
-  </si>
-  <si>
-    <t>A range plus a number</t>
-  </si>
-  <si>
-    <t>Adds 40 acres of summerfallow that is not in the table.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004A7C59"/>
       <sz val="14"/>
-      <color rgb="FF4A7C59"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="005C6B62"/>
       <sz val="10"/>
-      <color rgb="FF5C6B62"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="0024302A"/>
       <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <color rgb="002F5D46"/>
       <sz val="10"/>
-      <color rgb="FF2F5D46"/>
-      <name val="Consolas"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0024302A"/>
       <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A7C59"/>
+        <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6EFD9"/>
+        <fgColor rgb="00F6EFD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,47 +91,107 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -514,243 +479,319 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ranges and the SUM function</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Five fields of wheat.  Column B is the size of each field in acres and column C is its yield in bushels per acre.  Multiplying the two gives the bushels each field produced (column D).  To add those up we hand SUM a range — D5:D9 — rather than writing D5+D6+D7+D8+D9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Bushels</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>The formula in D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7" t="n">
         <v>52.4</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <f>B5*C5</f>
-        <v>6288</v>
-      </c>
-      <c r="E5" s="7" t="str">
-        <f t="shared" ref="E5:E10" ca="1" si="0">_xlfn.FORMULATEXT(D5)</f>
-        <v>=B5*C5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5">
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>_xlfn.FORMULATEXT(D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7" t="n">
         <v>48.9</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <f>B6*C6</f>
-        <v>11736</v>
-      </c>
-      <c r="E6" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>=B6*C6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5">
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>_xlfn.FORMULATEXT(D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7" t="n">
         <v>61.2</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <f>B7*C7</f>
-        <v>5814</v>
-      </c>
-      <c r="E7" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>=B7*C7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5">
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>_xlfn.FORMULATEXT(D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>310</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7" t="n">
         <v>55.7</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <f>B8*C8</f>
-        <v>17267</v>
-      </c>
-      <c r="E8" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>=B8*C8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5">
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>_xlfn.FORMULATEXT(D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>175</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7" t="n">
         <v>44.3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <f>B9*C9</f>
-        <v>7752.4999999999991</v>
-      </c>
-      <c r="E9" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>=B9*C9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="9">
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>_xlfn.FORMULATEXT(D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
         <f>SUM(B5:B9)</f>
-        <v>940</v>
-      </c>
-      <c r="D10" s="9">
+        <v/>
+      </c>
+      <c r="D10" s="10">
         <f>SUM(D5:D9)</f>
-        <v>48857.5</v>
-      </c>
-      <c r="E10" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>=SUM(D5:D9)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5">
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>_xlfn.FORMULATEXT(D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <f>AVERAGE(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f>AVERAGE(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Mean acres per field, and mean bushels per field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>COUNT(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>How many cells hold a NUMBER — blanks and text are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Other ways to give SUM a range</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>One column</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
         <f>SUM(B5:B9)</f>
-        <v>940</v>
-      </c>
-      <c r="C13" s="11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B13)</f>
-        <v>=SUM(B5:B9)</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="5">
+        <v/>
+      </c>
+      <c r="C15" s="8">
+        <f>_xlfn.FORMULATEXT(B15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The five acre figures, B5 down to B9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>One row</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
         <f>SUM(B5:D5)</f>
-        <v>6460.4</v>
-      </c>
-      <c r="C14" s="11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B14)</f>
-        <v>=SUM(B5:D5)</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="5">
+        <v/>
+      </c>
+      <c r="C16" s="8">
+        <f>_xlfn.FORMULATEXT(B16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Straight across row 5 — acres, yield and bushels. Rarely what you want.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Two ranges at once</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
         <f>SUM(B5:B9,D5:D9)</f>
-        <v>49797.5</v>
-      </c>
-      <c r="C15" s="11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B15)</f>
-        <v>=SUM(B5:B9,D5:D9)</v>
-      </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="5">
+        <v/>
+      </c>
+      <c r="C17" s="8">
+        <f>_xlfn.FORMULATEXT(B17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Separate ranges with a comma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A range plus a number</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
         <f>SUM(B5:B9,40)</f>
-        <v>980</v>
-      </c>
-      <c r="C16" s="11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B16)</f>
-        <v>=SUM(B5:B9,40)</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v/>
+      </c>
+      <c r="C18" s="8">
+        <f>_xlfn.FORMULATEXT(B18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Adds 40 acres of summerfallow that is not in the table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/textbook_examples/mod01_sum.xlsx
+++ b/textbook_examples/mod01_sum.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_2B591B77D540A71E1440B9B340ED90B65191EA02" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{619A3686-9717-F54A-8C64-11448E767E08}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_2B591B77D540A71E1440B9B340ED90B65191EA02" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B81896A-742F-B749-89F0-565439575A88}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete" sheetId="1" r:id="rId1"/>
-    <sheet name="Incomplete" sheetId="2" r:id="rId2"/>
+    <sheet name="Practice" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -244,13 +244,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -735,11 +735,11 @@
         <f>SUM(B2:B6)</f>
         <v>940</v>
       </c>
-      <c r="C12" s="11" t="str">
+      <c r="C12" s="12" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B12)</f>
         <v>=SUM(B2:B6)</v>
       </c>
-      <c r="D12" s="12"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="9" t="s">
         <v>23</v>
       </c>
@@ -752,11 +752,11 @@
         <f>SUM(B2:D2)</f>
         <v>6460.4</v>
       </c>
-      <c r="C13" s="11" t="str">
+      <c r="C13" s="12" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B13)</f>
         <v>=SUM(B2:D2)</v>
       </c>
-      <c r="D13" s="12"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="9" t="s">
         <v>18</v>
       </c>
@@ -769,11 +769,11 @@
         <f>SUM(B2:B6,D2:D6)</f>
         <v>49797.5</v>
       </c>
-      <c r="C14" s="11" t="str">
+      <c r="C14" s="12" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B14)</f>
         <v>=SUM(B2:B6,D2:D6)</v>
       </c>
-      <c r="D14" s="12"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
         <v>20</v>
       </c>
@@ -786,24 +786,24 @@
         <f>SUM(B2:B6,40)</f>
         <v>980</v>
       </c>
-      <c r="C15" s="11" t="str">
+      <c r="C15" s="12" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B15)</f>
         <v>=SUM(B2:B6,40)</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -842,7 +842,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -958,8 +958,8 @@
         <v>16</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="9" t="s">
         <v>23</v>
       </c>
@@ -969,8 +969,8 @@
         <v>17</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="9" t="s">
         <v>18</v>
       </c>
@@ -980,8 +980,8 @@
         <v>19</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
         <v>20</v>
       </c>
@@ -991,21 +991,21 @@
         <v>21</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
